--- a/data/trans_camb/IP16A09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Habitat-trans_camb.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 0,0</t>
+          <t>-7,62; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 3,54</t>
+          <t>-5,68; 3,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,28</t>
+          <t>0,0; 13,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 5,7</t>
+          <t>-1,89; 5,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,9</t>
+          <t>-2,99; 1,86</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 6,09</t>
+          <t>-3,79; 6,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 1,06</t>
+          <t>-6,57; 1,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,57</t>
+          <t>-1,88; 4,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,99</t>
+          <t>-3,79; 1,0</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,09; -1,09</t>
+          <t>-20,61; -0,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 0,94</t>
+          <t>-20,28; 1,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 2,5</t>
+          <t>-12,07; 2,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 14,78</t>
+          <t>-6,31; 14,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,3; -0,57</t>
+          <t>-11,44; -0,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 4,91</t>
+          <t>-8,85; 5,33</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,04</t>
+          <t>-100,0; 51,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 88,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 947,12</t>
+          <t>-90,7; 775,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-94,59; 2,96</t>
+          <t>-93,84; 21,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,33; 137,08</t>
+          <t>-78,05; 154,84</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 3,09</t>
+          <t>-12,33; 3,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 0,0</t>
+          <t>-16,82; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 7,14</t>
+          <t>-6,88; 6,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 0,0</t>
+          <t>-10,38; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 3,0</t>
+          <t>-5,4; 3,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,97; -1,0</t>
+          <t>-8,82; -1,0</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 315,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 0,45</t>
+          <t>-5,9; 0,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 0,06</t>
+          <t>-6,52; -0,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,39</t>
+          <t>-2,29; 3,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,4</t>
+          <t>-2,8; 2,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,4</t>
+          <t>-2,91; 1,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,33</t>
+          <t>-3,68; 0,22</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-87,28; 40,28</t>
+          <t>-90,45; 37,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-91,77; 34,91</t>
+          <t>-92,46; 5,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,65; 412,25</t>
+          <t>-63,48; 394,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,91; 312,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,8; 67,46</t>
+          <t>-65,08; 81,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,86; 29,26</t>
+          <t>-80,72; 24,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Habitat-trans_camb.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 0,0</t>
+          <t>-8,85; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 3,65</t>
+          <t>-5,57; 3,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,84</t>
+          <t>0,0; 14,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,68</t>
+          <t>-1,94; 5,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,86</t>
+          <t>-3,01; 1,91</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 6,18</t>
+          <t>-4,49; 6,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 1,07</t>
+          <t>-6,63; 1,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 6,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 4,65</t>
+          <t>-1,78; 4,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,0</t>
+          <t>-3,22; 1,01</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,61; -0,41</t>
+          <t>-20,88; -0,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 1,08</t>
+          <t>-21,04; 0,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 2,39</t>
+          <t>-11,17; 3,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 14,1</t>
+          <t>-5,2; 14,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,44; -0,19</t>
+          <t>-12,15; -0,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 5,33</t>
+          <t>-9,41; 4,64</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 88,48</t>
+          <t>-100,0; 100,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-90,7; 775,38</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-93,84; 21,23</t>
+          <t>-92,7; 17,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,05; 154,84</t>
+          <t>-78,51; 131,74</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 3,13</t>
+          <t>-13,3; 3,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 0,0</t>
+          <t>-15,5; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 6,51</t>
+          <t>-7,05; 6,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 0,0</t>
+          <t>-10,51; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 3,4</t>
+          <t>-5,91; 3,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -1,0</t>
+          <t>-10,56; -1,02</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 0,48</t>
+          <t>-5,82; 0,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,52; -0,37</t>
+          <t>-6,33; -0,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,57</t>
+          <t>-2,25; 3,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,39</t>
+          <t>-2,73; 2,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,36</t>
+          <t>-2,85; 1,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,22</t>
+          <t>-3,73; 0,34</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 37,26</t>
+          <t>-88,98; 41,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-92,46; 5,9</t>
+          <t>-92,51; 23,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,48; 394,01</t>
+          <t>-65,21; 446,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-84,91; 312,38</t>
+          <t>-82,4; 329,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 81,24</t>
+          <t>-66,28; 71,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,72; 24,51</t>
+          <t>-81,13; 33,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Habitat-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumieron medicamentos para los vómitos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-1,82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,08</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,16</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 0,0</t>
+          <t>0,0; 13,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 3,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,67</t>
+          <t>-8,01; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,64; 3,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,14</t>
+          <t>-1,95; 5,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,91</t>
+          <t>-2,98; 1,9</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-4,15%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-1,46</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 6,66</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>-3,84; 6,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,44; 1,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,31</t>
+          <t>-1,28; 4,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,01</t>
+          <t>-3,68; 0,99</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>22,18%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-57,99%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-8,38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-7,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,1</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,88; -0,16</t>
+          <t>-11,91; 2,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 0,96</t>
+          <t>-6,18; 14,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 3,06</t>
+          <t>-21,09; -1,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 14,75</t>
+          <t>-19,9; 0,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -0,25</t>
+          <t>-12,3; -0,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 4,64</t>
+          <t>-9,11; 4,91</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-56,27%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>56,78%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-76,37%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-69,03%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-56,27%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56,78%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 100,58</t>
+          <t>-100,0; 947,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 14,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-92,7; 17,33</t>
+          <t>-94,59; 2,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,51; 131,74</t>
+          <t>-81,33; 137,08</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,69</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,44</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-1,54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-3,09</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,44</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 3,09</t>
+          <t>-6,0; 7,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>-12,11; 0,0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>-12,4; 3,09</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>-15,5; 0,0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-7,05; 6,72</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-10,51; 0,0</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 3,41</t>
+          <t>-5,77; 3,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -1,02</t>
+          <t>-8,97; -1,0</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-49,84%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>20,07%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 315,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,38</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-2,28</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-2,75</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,44</t>
+          <t>-2,21; 3,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,33; -0,15</t>
+          <t>-3,09; 2,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 3,39</t>
+          <t>-5,45; 0,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,38</t>
+          <t>-6,23; 0,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 1,33</t>
+          <t>-2,98; 1,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,34</t>
+          <t>-3,62; 0,33</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>28,23%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-16,9%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-54,86%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-66,23%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-16,9%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-88,98; 41,58</t>
+          <t>-62,65; 412,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-92,51; 23,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,21; 446,31</t>
+          <t>-87,28; 40,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-82,4; 329,39</t>
+          <t>-91,77; 34,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,28; 71,83</t>
+          <t>-65,8; 67,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,13; 33,02</t>
+          <t>-81,86; 29,26</t>
         </is>
       </c>
     </row>
